--- a/Templates~/Config/Excels/__beans__.xlsx
+++ b/Templates~/Config/Excels/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Project Briseus\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Config\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D9EA47-D153-4419-B7F7-B1BC23D696E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52257CCF-7CB2-45BC-9087-9395FD37008B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="4755" windowWidth="28800" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="4980" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -96,10 +96,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>L10n.LocalizedStringBean</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ChineseSimplified</t>
   </si>
   <si>
@@ -123,27 +119,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>L10n.LocalizedImageBean</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L10n.LocalizedAudioBean</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>多语言字符串配置</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>多语言UI配置</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>多语言音频配置</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>##</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L10n.LocalizedBean</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -519,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
@@ -595,7 +579,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -624,107 +608,37 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="J7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Templates~/Config/Excels/__beans__.xlsx
+++ b/Templates~/Config/Excels/__beans__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Config\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Project Briseus\Config\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52257CCF-7CB2-45BC-9087-9395FD37008B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB9E551-22AA-4904-A2D4-1F7C640B16C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4980" yWindow="4980" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -119,15 +119,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>多语言字符串配置</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>##</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>L10n.LocalizedBean</t>
+    <t>支持的多语言</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L10n.LocalizationBean</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -579,7 +579,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -611,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>27</v>
